--- a/artfynd/A 46427-2025 artfynd.xlsx
+++ b/artfynd/A 46427-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132269738</v>
       </c>
       <c r="B2" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         <v>132351236</v>
       </c>
       <c r="B3" t="n">
-        <v>57894</v>
+        <v>57895</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 46427-2025 artfynd.xlsx
+++ b/artfynd/A 46427-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132269738</v>
       </c>
       <c r="B2" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         <v>132351236</v>
       </c>
       <c r="B3" t="n">
-        <v>57895</v>
+        <v>57899</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 46427-2025 artfynd.xlsx
+++ b/artfynd/A 46427-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132269738</v>
       </c>
       <c r="B2" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -801,7 +801,7 @@
         <v>132351236</v>
       </c>
       <c r="B3" t="n">
-        <v>57899</v>
+        <v>57900</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
